--- a/data/trans_dic/P21D_5_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,13; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,63</t>
+          <t>0,05; 0,57</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,33</t>
+          <t>0,2; 1,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,11</t>
+          <t>0,21; 1,08</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,54</t>
+          <t>0,04; 0,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,74</t>
+          <t>0,19; 0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,48</t>
+          <t>0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos</t>
+          <t>Población que, necesitando atención sanitaria psiquiátrica, no la pudo recibir por motivos económicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3826</t>
+          <t>0; 4086</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2870</t>
+          <t>0; 2916</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4485</t>
+          <t>0; 4562</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2960</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>610; 6310</t>
+          <t>580; 6015</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>401; 6974</t>
+          <t>522; 6303</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 4879</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1291</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5064</t>
+          <t>0; 5024</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5920</t>
+          <t>0; 6076</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>915; 6870</t>
+          <t>1060; 6962</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2026; 10249</t>
+          <t>1919; 9956</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>789; 8912</t>
+          <t>698; 9228</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2884; 11779</t>
+          <t>2979; 11657</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4642; 15567</t>
+          <t>5164; 16093</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21D_5_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P21D_5_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,35</t>
+          <t>0,14; 1,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,57</t>
+          <t>0,07; 0,73</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,35</t>
+          <t>0,25; 1,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,08</t>
+          <t>0,23; 1,16</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,55</t>
+          <t>0,06; 0,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,73</t>
+          <t>0,2; 0,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,49</t>
+          <t>0,17; 0,51</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>660</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>648</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1308</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4086</t>
+          <t>0; 4367</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2916</t>
+          <t>0; 3479</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4562</t>
+          <t>0; 4462</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2886</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>580; 6015</t>
+          <t>696; 7274</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>522; 6303</t>
+          <t>695; 7111</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4879</t>
+          <t>0; 5196</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5024</t>
+          <t>0; 5910</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4727</t>
+          <t>4876</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6076</t>
+          <t>0; 5864</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1060; 6962</t>
+          <t>1206; 7732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1919; 9956</t>
+          <t>2137; 10739</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5938</t>
+          <t>6679</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9319</t>
+          <t>10064</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>698; 9228</t>
+          <t>989; 8574</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2979; 11657</t>
+          <t>3369; 12548</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5164; 16093</t>
+          <t>5702; 16740</t>
         </is>
       </c>
     </row>
